--- a/samples/change_orders.xlsx
+++ b/samples/change_orders.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-28 14:37:15.381550</t>
+          <t>2026-01-29 14:12:19.381550</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-02-03 14:37:15.381550</t>
+          <t>2026-02-04 14:12:19.381550</t>
         </is>
       </c>
     </row>
@@ -505,37 +505,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Water allow attention floor stay successful career.
-Month whose various behavior window.
-Growth likely store least recent people item.
-Media sing every blood great attorney.</t>
+Month whose various behavior window.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wesley Montgomery</t>
+          <t>Andrew Crawford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-08-02 16:47:55.756929</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2024-10-22 16:47:55.756929</t>
-        </is>
-      </c>
+          <t>2024-08-03 16:22:59.756929</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -545,7 +539,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -555,22 +549,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Himself ground simply stop.
-Easy particular Republican quality ask exist break nice.
-Morning product point strategy result country.</t>
+          <t>Letter avoid see name body difficult media.
+Check organization theory participant leave.
+Contain feeling significant data boy easy.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jennifer Tanner</t>
+          <t>Dennis Lee</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2023-11-13 17:06:58.349159</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>2024-06-10 16:53:17.891043</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2024-07-23 16:53:17.891043</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,7 +578,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,10 +588,10 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Occur pull thought test.
-Off vote age power along simple.
-Voice away key concern set my.
-Road likely relate chance himself.</t>
+          <t>Series speech hard consumer.
+Seem notice old commercial my assume beyond.
+Company a respond control feeling off.
+Military rock culture.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -603,10 +601,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024-02-07 10:34:04.153946</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>2024-12-19 17:49:30.186899</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-04-05 17:49:30.186899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -626,89 +628,87 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Hot practice career high.
+Road likely relate chance himself.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lynn Gomez</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2023-06-20 07:52:38.213215</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2023-09-28 07:52:38.213215</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CO-000006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>American apply wish help floor prevent.
 Treatment arm easy home fill new drop.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Lynn Gomez</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2023-10-09 17:34:39.338488</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2024-01-17 17:34:39.338488</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CO-000006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sylvia Johnston</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2023-10-10 17:09:43.338488</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2024-01-30 17:09:43.338488</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CO-000007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Evening arm yes type majority article.
 Family join woman truth summer avoid.
 Out deal head far push adult need pick.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sylvia Johnston</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-02-13 00:14:09.432679</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-06-05 00:14:09.432679</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CO-000007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Serve build happen prevent important.
-Degree game choice many.
-Hope church us contain discussion.
-Former group security outside purpose.</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Melissa Osborne</t>
@@ -716,12 +716,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2024-02-10 15:10:21.248633</t>
+          <t>2026-02-13 23:49:13.432679</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2024-03-13 15:10:21.248633</t>
+          <t>2026-03-17 23:49:13.432679</t>
         </is>
       </c>
     </row>
@@ -743,8 +743,8 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>National option perhaps indeed small international wish.
-Conference remain somebody very it by.</t>
+          <t>Serve build happen prevent important.
+Degree game choice many.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022-11-10 13:15:26.642472</t>
+          <t>2024-02-11 14:45:25.248633</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -777,10 +777,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Focus out property.
-Peace blood million candidate off.
-Happy executive involve win those.
-Former industry game deal work.</t>
+          <t>Experience budget forget father.
+Former group security outside purpose.
+Make little even drive.
+Loss pressure use morning conference remain.
+Very it by radio.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -790,12 +791,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-04-02 23:11:06.441168</t>
+          <t>2023-07-20 06:30:15.644673</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-04-25 23:11:06.441168</t>
+          <t>2023-08-12 06:30:15.644673</t>
         </is>
       </c>
     </row>
@@ -817,7 +818,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rather yeah spend place child.</t>
+          <t>Specific student attorney peace blood million.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -827,7 +828,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2023-12-04 04:23:49.677465</t>
+          <t>2025-09-05 20:08:12.924713</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -850,8 +851,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Executive news dog choice.
-Church them within she significant.</t>
+          <t>Everything major perform site leg.
+Despite feel fire glass.
+Work glass ability early.
+Place child when because executive news dog.
+Treatment still church them.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -861,7 +865,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-10 20:50:55.696684</t>
+          <t>2023-01-18 22:13:07.459168</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -884,9 +888,10 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Little could strong hospital poor how.
-Foot team the plant available view.
-Board war rather democratic.</t>
+          <t>Able forget education say.
+Hospital poor how wife foot team the plant.
+Drive instead board war.
+Democratic senior property far.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -896,12 +901,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2023-01-02 19:09:53.492593</t>
+          <t>2026-06-09 20:31:45.876507</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023-03-13 19:09:53.492593</t>
+          <t>2026-08-18 20:31:45.876507</t>
         </is>
       </c>
     </row>
@@ -923,7 +928,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Home yes skill thus as see.</t>
+          <t>Arrive campaign evening affect.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -933,12 +938,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-07-17 18:41:07.744116</t>
+          <t>2024-01-31 22:29:25.951699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2025-09-04 18:41:07.744116</t>
+          <t>2024-03-20 22:29:25.951699</t>
         </is>
       </c>
     </row>
@@ -960,7 +965,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Already receive side.</t>
+          <t>Could mention view hospital think stop member.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -970,12 +975,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2023-11-16 03:26:05.566806</t>
+          <t>2025-06-10 15:03:28.821091</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2024-03-01 03:26:05.566806</t>
+          <t>2025-09-24 15:03:28.821091</t>
         </is>
       </c>
     </row>
@@ -997,8 +1002,8 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>View hospital think stop member indicate.
-Perhaps experience thus hospital also significant change.</t>
+          <t>Wonder economy always enough bit when fly whether.
+Computer few owner hard.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1008,12 +1013,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2023-04-11 16:18:31.652996</t>
+          <t>2024-03-12 09:02:13.907228</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2023-06-14 16:18:31.652996</t>
+          <t>2024-05-15 09:02:13.907228</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1040,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Final animal alone item.</t>
+          <t>Question guy cell place item growth.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1045,12 +1050,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-12-07 22:26:58.986218</t>
+          <t>2023-04-15 10:22:22.150562</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-03 22:26:58.986218</t>
+          <t>2023-08-10 10:22:22.150562</t>
         </is>
       </c>
     </row>
@@ -1072,8 +1077,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Question guy cell place item growth.
-Office he name view.</t>
+          <t>He name view clearly reach well provide.
+Form friend responsibility follow.
+Room west charge your television great.
+Necessary light worker increase move total range.
+Easy appear interview part.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1083,12 +1091,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024-11-25 00:30:17.414139</t>
+          <t>2026-05-05 09:54:56.291142</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-01-27 00:30:17.414139</t>
+          <t>2026-07-07 09:54:56.291142</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1118,8 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Blue some mission cost region then room west.</t>
+          <t>Yourself break fill local operation green small.
+Now since treat nothing.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1120,7 +1129,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2023-03-08 18:34:10.988448</t>
+          <t>2026-04-05 18:55:10.002856</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1143,7 +1152,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Great Mr structure seem member create.</t>
+          <t>Notice instead start difficult mission seem summer.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1153,12 +1162,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2023-02-19 06:31:53.511035</t>
+          <t>2023-02-02 01:40:33.385047</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2023-03-13 06:31:53.511035</t>
+          <t>2023-02-24 01:40:33.385047</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1189,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Office rest man yard growth.</t>
+          <t>Ok describe within water.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1190,12 +1199,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024-07-11 11:24:56.735079</t>
+          <t>2026-01-03 11:23:56.360620</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2024-07-27 11:24:56.735079</t>
+          <t>2026-01-19 11:23:56.360620</t>
         </is>
       </c>
     </row>
@@ -1207,32 +1216,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>In-Work</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>So nor before laugh.
-Small blood indicate listen building three discussion put.
-Little medical whether area politics market.</t>
+          <t>Whatever nice measure reality how concern issue.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Justin Baldwin</t>
+          <t>Joshua Johnson</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024-02-13 16:20:03.508042</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>2025-08-12 18:46:42.224580</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-09-01 18:46:42.224580</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1242,17 +1253,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in-review</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Consumer growth system however customer.</t>
+          <t>Worry research different system member drug.
+Set small yeah material.
+Sing suddenly member five push.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1262,7 +1275,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-23 18:19:25.079774</t>
+          <t>2023-05-03 18:30:00.584309</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1285,10 +1298,10 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nice measure reality how.
-Occur evidence write property.
-Focus speech best experience wonder site.
-Set small yeah material.</t>
+          <t>Shake campaign when staff computer.
+Line although subject window light feeling PM.
+Conference throughout test blue white senior sing.
+Stay trouble mind wear.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1298,12 +1311,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2023-09-12 14:28:43.158573</t>
+          <t>2023-11-30 08:19:10.410826</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2023-10-28 14:28:43.158573</t>
+          <t>2024-02-14 08:19:10.410826</t>
         </is>
       </c>
     </row>
@@ -1325,10 +1338,9 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Member five push.
-Ago stock shake campaign when staff.
-Short line although subject.
-Industry back feeling conference throughout test blue.</t>
+          <t>Second unit economy art seven.
+Less difficult these wrong score region pass.
+Hard agency statement reveal tough find.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1338,7 +1350,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-01-31 05:52:05.761545</t>
+          <t>2026-05-18 23:56:40.755691</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1361,8 +1373,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sound stay trouble mind wear.
-Fast there my in throughout.</t>
+          <t>Building open clear pay.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1372,12 +1383,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-17 22:18:01.940652</t>
+          <t>2026-05-15 12:43:30.980494</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-27 22:18:01.940652</t>
+          <t>2026-08-25 12:43:30.980494</t>
         </is>
       </c>
     </row>
@@ -1399,9 +1410,9 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Difficult these wrong score.
-Moment hard agency statement reveal tough find whether.
-Born produce avoid along tax.</t>
+          <t>Black time kind mean middle deep state.
+Wrong while discuss still.
+Positive because trade drop soldier.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1411,7 +1422,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2023-01-20 04:58:38.999379</t>
+          <t>2022-09-10 09:25:43.680968</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1434,7 +1445,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wind part player information.</t>
+          <t>Pass crime respond risk test deep.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1444,7 +1455,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-02-19 19:07:29.497483</t>
+          <t>2022-11-22 21:30:59.381823</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1457,7 +1468,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>in_review</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1467,21 +1478,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>While discuss still yes positive because trade drop.
-Before movement together.</t>
+          <t>Strong vote fast American.
+Interesting see herself employee.
+Possible staff compare pressure part high.
+Voice control treat edge pretty six.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Joshua Johnson</t>
+          <t>Jennifer Carpenter</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-01-26 05:45:43.894764</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>2026-04-27 04:56:48.419268</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-24 04:56:48.419268</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1491,7 +1508,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>in-review</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,9 +1518,10 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Respond risk test deep way situation.
-Strong vote fast American.
-Interesting see herself employee.</t>
+          <t>Case book federal card.
+Bad property information news apply cultural about.
+Play human produce board.
+Couple environmental kind get although.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1513,14 +1531,10 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024-12-24 09:59:20.293730</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2025-04-17 09:59:20.293730</t>
-        </is>
-      </c>
+          <t>2022-12-01 21:40:26.392157</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1540,7 +1554,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Make hear week in.</t>
+          <t>Probably war employee responsibility defense chair.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1550,7 +1564,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2023-11-06 02:49:56.526746</t>
+          <t>2025-07-08 08:46:43.954495</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1573,8 +1587,9 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Treat edge pretty six best stay.
-Case book federal card.</t>
+          <t>Agreement sit his friend blue international.
+Less lead election popular should whatever.
+Section food buy along main financial arm range.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1584,12 +1599,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2023-12-11 00:33:54.058094</t>
+          <t>2023-10-25 14:55:17.352480</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2023-11-30 00:33:54.058094</t>
+          <t>2023-10-14 14:55:17.352480</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1626,8 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Future cell suffer practice debate play.</t>
+          <t>Cover energy history candidate.
+Than nature themselves per discussion sign choose great.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1621,7 +1637,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2024-08-05 11:24:10.159406</t>
+          <t>2025-07-23 13:49:41.517858</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1644,7 +1660,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Story debate win arrive.</t>
+          <t>Result dream consider them consider fact hour.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1654,7 +1670,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-02-13 16:01:36.180352</t>
+          <t>2023-03-17 03:34:06.445513</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1677,7 +1693,9 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Security fine probably war employee responsibility defense.</t>
+          <t>Court mention economic.
+Evidence art mouth doctor best image.
+Court say between defense.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1687,12 +1705,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2022-08-31 08:21:46.123763</t>
+          <t>2023-02-01 12:44:42.278948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2022-09-25 08:21:46.123763</t>
+          <t>2023-02-26 12:44:42.278948</t>
         </is>
       </c>
     </row>
@@ -1714,9 +1732,9 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Someone agreement sit his friend blue.
-Commercial less lead election popular should.
-Section food buy along main financial arm range.</t>
+          <t>Candidate smile where long consider half hold.
+Here research drug analysis certainly keep.
+Position pick well modern explain nature.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1726,12 +1744,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2023-02-11 05:48:50.321009</t>
+          <t>2026-06-27 02:08:23.615378</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2023-03-25 05:48:50.321009</t>
+          <t>2026-08-08 02:08:23.615378</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1771,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cover energy history candidate.</t>
+          <t>Standard time tend leader.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1763,12 +1781,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-07-22 14:14:37.517858</t>
+          <t>2022-10-15 23:22:27.293649</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025-08-13 14:14:37.517858</t>
+          <t>2022-11-06 23:22:27.293649</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1808,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Until second hair success effort official environmental.</t>
+          <t>Sense change allow become order responsibility her.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1800,12 +1818,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024-11-26 16:11:27.168071</t>
+          <t>2023-11-14 09:34:28.876514</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-02-28 16:11:27.168071</t>
+          <t>2024-02-16 09:34:28.876514</t>
         </is>
       </c>
     </row>
@@ -1827,9 +1845,8 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Dream consider them consider fact hour.
-Finally sometimes court mention.
-Piece they evidence art mouth.</t>
+          <t>First Mrs ready.
+Popular behind air tree anything let.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1839,12 +1856,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-06-23 13:42:24.141813</t>
+          <t>2023-07-22 01:14:05.914087</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-05-31 13:42:24.141813</t>
+          <t>2023-06-29 01:14:05.914087</t>
         </is>
       </c>
     </row>
@@ -1866,8 +1883,8 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Technology court say between defense wrong.
-Music quickly do write skin customer actually.</t>
+          <t>Above which perform floor American quite mother.
+Peace meet site his line.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1877,12 +1894,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2023-06-19 00:38:14.060127</t>
+          <t>2023-10-24 03:31:22.234851</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2023-10-10 00:38:14.060127</t>
+          <t>2024-02-14 03:31:22.234851</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1921,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Research drug analysis certainly keep stage position.</t>
+          <t>Thousand would age hot.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1914,12 +1931,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2023-02-12 14:20:09.716957</t>
+          <t>2025-05-31 00:43:31.644375</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2023-03-17 14:20:09.716957</t>
+          <t>2025-07-03 00:43:31.644375</t>
         </is>
       </c>
     </row>
@@ -1941,8 +1958,8 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Care car bill hotel case cup strong.
-Leader friend enough sense change allow.</t>
+          <t>Human include these take hotel indicate international.
+Population fear stage eight hospital view nor teacher.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1952,7 +1969,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-01-15 06:13:29.406902</t>
+          <t>2022-11-02 15:04:17.055074</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1975,10 +1992,8 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Her eight soon single first.
-Other look popular behind air tree anything.
-Year second shake last expect technology sense.
-Prevent energy agent.</t>
+          <t>Candidate big idea direction couple rule.
+Prepare improve cold away.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1988,12 +2003,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2022-11-19 04:24:07.368827</t>
+          <t>2024-05-10 07:25:37.545346</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2022-11-24 04:24:07.368827</t>
+          <t>2024-05-15 07:25:37.545346</t>
         </is>
       </c>
     </row>
@@ -2015,11 +2030,9 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Meet site his line return.
-Ten thousand would age hot back look.
-Maintain tax member page something seat.
-Population fear stage eight hospital view nor teacher.
-Like population trade candidate big idea direction.</t>
+          <t>Go without ten job special.
+Long indeed second bag discuss minute enough clearly.
+Step church campaign general help sing.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2029,7 +2042,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-03-05 09:25:26.912190</t>
+          <t>2023-06-19 07:47:50.487398</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2052,7 +2065,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Prepare improve cold away.</t>
+          <t>Voice brother one drive election simply store.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2062,12 +2075,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2023-04-15 12:36:06.227547</t>
+          <t>2023-05-31 15:17:16.825726</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2023-06-24 12:36:06.227547</t>
+          <t>2023-08-09 15:17:16.825726</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2102,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Go without ten job special.</t>
+          <t>People through stage page letter hour.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2099,12 +2112,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2023-06-18 08:12:46.487398</t>
+          <t>2022-07-18 21:30:25.013004</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2023-09-19 08:12:46.487398</t>
+          <t>2022-10-19 21:30:25.013004</t>
         </is>
       </c>
     </row>
@@ -2126,10 +2139,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Second bag discuss minute enough.
-Board step church campaign.
-Impact glass chance traditional least force.
-Trade expert popular may suffer thousand that people.</t>
+          <t>Civil throughout indicate myself close model two.
+Western stock black hope.
+Last significant goal me her respond people above.
+In market up care arrive American may political.
+Check behind front government truth service result face.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2139,12 +2153,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2024-12-05 00:41:46.376047</t>
+          <t>2025-10-31 22:53:03.873883</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025-01-20 00:41:46.376047</t>
+          <t>2025-12-16 22:53:03.873883</t>
         </is>
       </c>
     </row>
@@ -2166,11 +2180,9 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tree various recently act loss west PM size.
-Close model two card.
-Stock black hope past hard.
-Continue TV deep write born outside.
-Which family child although consumer chance.</t>
+          <t>Win seem matter anything husband.
+Western each analysis certain ready ahead.
+Goal left human else management maybe effort.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2180,7 +2192,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-01 12:31:31.129110</t>
+          <t>2024-12-04 14:44:10.803023</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2203,10 +2215,8 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Check behind front government truth service result face.
-Example dinner win seem matter anything husband hit.
-Loss according down media approach.
-Discuss total concern laugh may idea.</t>
+          <t>Score site by stock certainly bring.
+Effect myself because major phone.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2216,12 +2226,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2025-04-22 14:21:35.054613</t>
+          <t>2023-04-16 05:14:04.369142</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2025-08-17 14:21:35.054613</t>
+          <t>2023-08-11 05:14:04.369142</t>
         </is>
       </c>
     </row>
@@ -2243,9 +2253,8 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Score site by stock certainly bring.
-Effect myself because major phone.
-Skill still generation bag.</t>
+          <t>Still generation bag daughter friend.
+Guess cold skin go PM.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2255,12 +2264,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2023-03-07 11:52:47.945730</t>
+          <t>2025-04-06 20:40:56.957983</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2023-05-04 11:52:47.945730</t>
+          <t>2025-06-03 20:40:56.957983</t>
         </is>
       </c>
     </row>
@@ -2282,10 +2291,10 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Guess cold skin go PM.
-Few most market public.
-Care wrong manager matter huge magazine.
-Fish father system even with.</t>
+          <t>Nearly establish information care wrong manager matter.
+Buy add fish father system even.
+Until learn reflect situation.
+Difference public capital together herself administration in.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2295,12 +2304,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2023-05-05 20:26:39.906837</t>
+          <t>2023-01-10 13:49:40.953489</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2023-08-27 20:26:39.906837</t>
+          <t>2023-05-04 13:49:40.953489</t>
         </is>
       </c>
     </row>
@@ -2322,8 +2331,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Reflect situation work difference public capital together.
-Article space seek trouble suffer degree.</t>
+          <t>Theory fly attack can soldier.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2333,12 +2341,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26 19:15:40.688026</t>
+          <t>2025-02-04 16:23:28.823934</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-29 19:15:40.688026</t>
+          <t>2025-04-09 16:23:28.823934</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Attack can soldier conference there bed live.</t>
+          <t>Live meeting successful.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2370,12 +2378,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-11 10:47:09.737506</t>
+          <t>2023-03-31 18:28:24.788382</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-02-06 10:47:09.737506</t>
+          <t>2023-04-26 18:28:24.788382</t>
         </is>
       </c>
     </row>
@@ -2397,8 +2405,9 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Within red meeting difficult reduce floor natural.
-Face reach law recent.</t>
+          <t>Meeting difficult reduce floor.
+Town close government need surface something chair.
+Set career record always despite them next.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2408,12 +2417,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2024-07-24 02:20:18.811901</t>
+          <t>2025-07-22 20:00:16.218572</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2024-10-21 02:20:18.811901</t>
+          <t>2025-10-19 20:00:16.218572</t>
         </is>
       </c>
     </row>
@@ -2435,8 +2444,8 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Set career record always despite them next.
-Debate kitchen herself pattern.</t>
+          <t>Kitchen herself pattern threat describe simple forget.
+Hot throughout reveal.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2446,12 +2455,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-04-19 16:50:18.567322</t>
+          <t>2025-03-15 21:26:31.472217</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2025-05-31 16:50:18.567322</t>
+          <t>2025-04-26 21:26:31.472217</t>
         </is>
       </c>
     </row>
@@ -2473,9 +2482,9 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Simple forget along few behind.
-Sit student approach body arm.
-Unit inside quickly prevent film.</t>
+          <t>Approach body arm decision.
+Inside quickly prevent film.
+Guy include mother accept dinner energy.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2485,7 +2494,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-30 15:50:44.213871</t>
+          <t>2025-01-31 12:09:09.772119</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2508,9 +2517,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Catch nor management Congress gun price.
-Democratic investment growth either cost.
-Woman go crime without race.</t>
+          <t>Democratic investment growth either cost.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2520,7 +2527,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-29 16:01:18.035693</t>
+          <t>2024-03-28 19:26:49.098994</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2543,7 +2550,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Current suffer analysis receive her more feeling.</t>
+          <t>Network let executive sister resource move.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2553,12 +2560,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2024-12-12 16:03:49.790986</t>
+          <t>2025-03-26 04:54:12.882546</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2024-12-16 16:03:49.790986</t>
+          <t>2025-03-30 04:54:12.882546</t>
         </is>
       </c>
     </row>
@@ -2580,11 +2587,8 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Rich state meet reality sometimes.
-Final use civil like season reduce.
-Paper another just cause must.
-Including population culture have.
-Country month we fact near.</t>
+          <t>Receive her more feeling simply who spring.
+Teach can carry final use civil like.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2594,12 +2598,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-08-17 11:21:16.839830</t>
+          <t>2025-03-22 05:30:45.890515</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2025-07-21 11:21:16.839830</t>
+          <t>2025-02-23 05:30:45.890515</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2625,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Deal exist dream sure step list fact check.</t>
+          <t>Paper another just cause must.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2631,12 +2635,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2024-09-08 20:04:42.359095</t>
+          <t>2025-07-03 01:42:51.077773</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2024-11-11 20:04:42.359095</t>
+          <t>2025-09-05 01:42:51.077773</t>
         </is>
       </c>
     </row>
@@ -2658,8 +2662,9 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fish discuss color month item where.
-Whatever of base.</t>
+          <t>Population culture have director on sell.
+Fact near must to.
+Deal exist dream sure step list fact check.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2669,12 +2674,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2023-08-19 01:59:05.693825</t>
+          <t>2025-08-30 01:38:56.285241</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2023-11-27 01:59:05.693825</t>
+          <t>2025-12-08 01:38:56.285241</t>
         </is>
       </c>
     </row>
@@ -2696,8 +2701,9 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Job fund back individual month pretty.
-Forget direction base.</t>
+          <t>Fish discuss color month item where.
+Whatever of base.
+About job fund back individual.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2707,12 +2713,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-09-19 16:40:22.976697</t>
+          <t>2023-08-20 01:34:09.693825</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2025-10-22 16:40:22.976697</t>
+          <t>2023-09-22 01:34:09.693825</t>
         </is>
       </c>
     </row>
@@ -2734,10 +2740,8 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Beautiful site herself organization machine.
-Person station determine five.
-Film white important travel management evening again.
-Hour always newspaper doctor program.</t>
+          <t>Forget direction base.
+Task on either rock operation care.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2747,12 +2751,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2024-04-17 00:03:16.555926</t>
+          <t>2024-08-21 04:59:23.774180</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2024-05-15 00:03:16.555926</t>
+          <t>2024-09-18 04:59:23.774180</t>
         </is>
       </c>
     </row>
@@ -2774,8 +2778,8 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>May administration similar billion.
-Sister operation whatever economic.</t>
+          <t>Person station determine five.
+Film white important travel management evening again.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2785,7 +2789,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-11-10 11:05:49.747921</t>
+          <t>2025-11-07 19:32:55.967941</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2808,7 +2812,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Accept majority add capital.</t>
+          <t>Newspaper doctor program once official may.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2818,12 +2822,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-15 21:04:01.683105</t>
+          <t>2023-04-30 08:37:05.392192</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-30 21:04:01.683105</t>
+          <t>2023-05-15 08:37:05.392192</t>
         </is>
       </c>
     </row>
@@ -2845,8 +2849,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Throw politics share sell indeed open.
-Financial avoid many entire resource picture.</t>
+          <t>And sister operation whatever.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2856,12 +2859,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-12-29 00:32:39.848915</t>
+          <t>2022-08-05 07:47:58.452560</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:39.848915</t>
+          <t>2022-10-10 07:47:58.452560</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Play seem least.</t>
+          <t>Community paper there oil list nation herself.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2893,12 +2896,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2024-07-20 20:51:00.479587</t>
+          <t>2023-07-12 02:36:26.179312</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2024-08-19 20:51:00.479587</t>
+          <t>2023-08-11 02:36:26.179312</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2923,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bar draw deal then.</t>
+          <t>Indeed open reality financial avoid many.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2930,7 +2933,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-05-29 20:41:48.743670</t>
+          <t>2026-02-05 09:19:01.760632</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2953,9 +2956,10 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Range article industry recently also exist with.
-Thousand conference girl popular officer.
-Hit ball each.</t>
+          <t>Quickly again growth water talk most site.
+Begin face response country general Mrs my air.
+Carry medical sit glass plan explain.
+Conference girl popular officer administration sit administration.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2965,12 +2969,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2023-01-28 21:13:09.250533</t>
+          <t>2023-08-05 10:09:52.722428</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2023-04-17 21:13:09.250533</t>
+          <t>2023-10-23 10:09:52.722428</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3006,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2023-03-01 04:19:26.288098</t>
+          <t>2026-06-25 23:50:41.384440</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3039,7 +3043,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2022-11-20 12:46:28.696041</t>
+          <t>2022-11-21 12:21:32.696041</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3073,12 +3077,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-02-27 11:26:31.056258</t>
+          <t>2025-02-28 11:01:35.056258</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2025-05-03 11:26:31.056258</t>
+          <t>2025-05-04 11:01:35.056258</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3115,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-20 03:37:38.831248</t>
+          <t>2026-02-21 03:12:42.831248</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-10 03:37:38.831248</t>
+          <t>2026-04-11 03:12:42.831248</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3153,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2023-01-25 02:38:19.516469</t>
+          <t>2023-01-26 02:13:23.516469</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3183,12 +3187,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2022-11-05 04:08:53.132209</t>
+          <t>2022-11-06 03:43:57.132209</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2022-12-14 04:08:53.132209</t>
+          <t>2022-12-15 03:43:57.132209</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3224,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2022-09-17 00:16:42.379438</t>
+          <t>2022-09-17 23:51:46.379438</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3233,7 +3237,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3254,12 +3258,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2024-03-04 11:49:54.236057</t>
+          <t>2024-03-05 11:24:58.236057</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2024-04-15 11:49:54.236057</t>
+          <t>2024-04-16 11:24:58.236057</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3298,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024-08-15 16:55:35.564176</t>
+          <t>2024-08-16 16:30:39.564176</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -3328,12 +3332,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-19 13:47:53.590949</t>
+          <t>2026-02-20 13:22:57.590949</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-01-29 13:47:53.590949</t>
+          <t>2026-01-30 13:22:57.590949</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3369,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024-12-02 12:42:09.467955</t>
+          <t>2024-12-03 12:17:13.467955</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-10-04 17:21:23.771985</t>
+          <t>2025-10-05 16:56:27.771985</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3432,12 +3436,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-04-08 03:26:19.932074</t>
+          <t>2025-04-09 03:01:23.932074</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2025-06-30 03:26:19.932074</t>
+          <t>2025-07-01 03:01:23.932074</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3475,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-09-05 14:46:25.698622</t>
+          <t>2024-09-06 14:21:29.698622</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3507,12 +3511,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-06-08 04:15:23.171546</t>
+          <t>2025-06-09 03:50:27.171546</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2025-09-14 04:15:23.171546</t>
+          <t>2025-09-15 03:50:27.171546</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3550,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2023-06-19 01:53:45.150465</t>
+          <t>2023-06-20 01:28:49.150465</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2023-10-09 01:53:45.150465</t>
+          <t>2023-10-10 01:28:49.150465</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3588,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-11-03 01:23:18.117988</t>
+          <t>2025-11-04 00:58:22.117988</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2025-11-25 01:23:18.117988</t>
+          <t>2025-11-26 00:58:22.117988</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3627,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2023-02-11 11:44:35.009260</t>
+          <t>2023-02-12 11:19:39.009260</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3658,12 +3662,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-16 16:04:49.846151</t>
+          <t>2026-03-17 15:39:53.846151</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-08 16:04:49.846151</t>
+          <t>2026-03-09 15:39:53.846151</t>
         </is>
       </c>
     </row>
@@ -3696,12 +3700,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2023-11-01 00:43:46.816671</t>
+          <t>2023-11-02 00:18:50.816671</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2024-01-09 00:43:46.816671</t>
+          <t>2024-01-10 00:18:50.816671</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3738,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-03-05 17:04:13.920630</t>
+          <t>2025-03-06 16:39:17.920630</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3767,12 +3771,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-25 05:52:35.712149</t>
+          <t>2026-02-26 05:27:39.712149</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-05-06 05:52:35.712149</t>
+          <t>2026-05-07 05:27:39.712149</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3808,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2023-10-15 13:35:18.413440</t>
+          <t>2023-10-16 13:10:22.413440</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2023-11-03 13:35:18.413440</t>
+          <t>2023-11-04 13:10:22.413440</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3846,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2023-11-06 13:21:32.564567</t>
+          <t>2023-11-07 12:56:36.564567</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2024-02-29 13:21:32.564567</t>
+          <t>2024-03-01 12:56:36.564567</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3883,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-10 14:05:14.427251</t>
+          <t>2026-06-11 13:40:18.427251</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -3913,7 +3917,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024-11-30 12:50:06.458776</t>
+          <t>2024-12-01 12:25:10.458776</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -3946,7 +3950,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2023-08-12 19:57:46.583913</t>
+          <t>2023-08-13 19:32:50.583913</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -3979,7 +3983,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-09-21 02:10:36.493186</t>
+          <t>2024-09-22 01:45:40.493186</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -4012,12 +4016,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-18 04:06:45.853753</t>
+          <t>2026-04-19 03:41:49.853753</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-29 04:06:45.853753</t>
+          <t>2026-07-30 03:41:49.853753</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2025-04-29 10:14:38.786416</t>
+          <t>2025-04-30 09:49:42.786416</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -4085,7 +4089,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2023-12-15 14:09:56.446958</t>
+          <t>2023-12-16 13:45:00.446958</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4118,7 +4122,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2025-07-02 04:19:10.763175</t>
+          <t>2025-07-03 03:54:14.763175</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -4152,12 +4156,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2024-09-28 06:11:59.002427</t>
+          <t>2024-09-29 05:47:03.002427</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2025-01-07 06:11:59.002427</t>
+          <t>2025-01-08 05:47:03.002427</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4196,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2024-08-08 15:27:07.086967</t>
+          <t>2024-08-09 15:02:11.086967</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2024-08-11 15:27:07.086967</t>
+          <t>2024-08-12 15:02:11.086967</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2023-03-07 01:09:24.701839</t>
+          <t>2023-03-08 00:44:28.701839</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2023-06-25 01:09:24.701839</t>
+          <t>2023-06-26 00:44:28.701839</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4273,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2023-06-04 23:23:02.650859</t>
+          <t>2023-06-05 22:58:06.650859</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2023-09-15 23:23:02.650859</t>
+          <t>2023-09-16 22:58:06.650859</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4310,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2024-05-31 17:16:57.003952</t>
+          <t>2024-06-01 16:52:01.003952</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2024-09-07 17:16:57.003952</t>
+          <t>2024-09-08 16:52:01.003952</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2025-01-14 01:27:18.072782</t>
+          <t>2025-01-15 01:02:22.072782</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -4378,12 +4382,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2025-08-07 06:04:40.197033</t>
+          <t>2025-08-08 05:39:44.197033</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2025-08-29 06:04:40.197033</t>
+          <t>2025-08-30 05:39:44.197033</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2022-11-17 09:32:05.780179</t>
+          <t>2022-11-18 09:07:09.780179</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -4449,12 +4453,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2023-04-17 15:05:45.536452</t>
+          <t>2023-04-18 14:40:49.536452</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2023-07-07 15:05:45.536452</t>
+          <t>2023-07-08 14:40:49.536452</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4491,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2023-02-26 09:31:37.833365</t>
+          <t>2023-02-27 09:06:41.833365</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -4520,7 +4524,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2025-06-03 10:00:09.570533</t>
+          <t>2025-06-04 09:35:13.570533</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -4553,12 +4557,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2024-09-25 04:40:29.380449</t>
+          <t>2024-09-26 04:15:33.380449</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2025-01-03 04:40:29.380449</t>
+          <t>2025-01-04 04:15:33.380449</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4594,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2024-03-31 07:29:24.668163</t>
+          <t>2024-04-01 07:04:28.668163</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -4625,12 +4629,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2023-01-05 11:59:09.653318</t>
+          <t>2023-01-06 11:34:13.653318</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2023-04-10 11:59:09.653318</t>
+          <t>2023-04-11 11:34:13.653318</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4666,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2022-08-12 01:05:56.306814</t>
+          <t>2022-08-13 00:41:00.306814</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -4697,12 +4701,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-21 01:32:48.478104</t>
+          <t>2026-05-22 01:07:52.478104</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-06-08 01:32:48.478104</t>
+          <t>2026-06-09 01:07:52.478104</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4739,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2025-09-14 01:24:12.331611</t>
+          <t>2025-09-15 00:59:16.331611</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2025-12-22 01:24:12.331611</t>
+          <t>2025-12-23 00:59:16.331611</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4776,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2023-04-01 11:50:51.676369</t>
+          <t>2023-04-02 11:25:55.676369</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2023-06-19 11:50:51.676369</t>
+          <t>2023-06-20 11:25:55.676369</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2024-03-11 12:21:49.382920</t>
+          <t>2024-03-12 11:56:53.382920</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4823,7 +4827,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4833,25 +4837,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Science authority space less contain month.
-Along serious imagine my nation decade.</t>
+          <t>Science authority space less contain month.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wesley Montgomery</t>
+          <t>Joshua Johnson</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2023-08-20 20:16:34.847611</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>2023-10-05 20:16:34.847611</t>
-        </is>
-      </c>
+          <t>2023-08-21 19:51:38.847611</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4861,30 +4860,35 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>in-review</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Foot goal garden hit mind.</t>
+          <t>Serious imagine my nation.
+Street too idea foot goal.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jennifer Carpenter</t>
+          <t>Jordan Fitzgerald</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2025-01-07 14:27:12.962456</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>2025-01-27 11:33:16.978515</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2025-05-23 11:33:16.978515</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4894,7 +4898,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>in-review</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4904,25 +4908,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Off table break support ten.
-Six by TV challenge miss.</t>
+          <t>Mind stop lose off table break support ten.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Melanie Rogers</t>
+          <t>Jennifer Tanner</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2025-11-04 04:22:22.912097</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2026-02-03 04:22:22.912097</t>
-        </is>
-      </c>
+          <t>2023-11-24 02:50:02.161924</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4932,31 +4931,36 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Identify example mind trip rule board something.
-A blood meet identify step will.</t>
+          <t>Tv challenge miss mean.
+Player themselves media quality.
+Major beat call speak agency a blood.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Melanie Rogers</t>
+          <t>Jordan Fitzgerald</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2024-07-17 07:38:08.780664</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+          <t>2023-09-27 07:05:02.052424</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2023-10-01 07:05:02.052424</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4971,29 +4975,28 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>South here admit something major.
-Until away carry cause rise piece local.
-Skin realize push common style like soon.</t>
+          <t>Step will know sign major south here admit.
+Major office offer certain wonder check.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Justin Baldwin</t>
+          <t>Sylvia Johnston</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2024-04-20 08:10:35.359256</t>
+          <t>2024-07-24 09:58:02.400772</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2024-05-13 08:10:35.359256</t>
+          <t>2024-09-26 09:58:02.400772</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5018,8 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>There design apply either mention catch word true.</t>
+          <t>In skin realize push common style like.
+Whatever yes operation.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5025,12 +5029,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2022-08-29 01:40:09.647122</t>
+          <t>2025-05-18 04:45:40.176254</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2022-11-24 01:40:09.647122</t>
+          <t>2025-08-21 04:45:40.176254</t>
         </is>
       </c>
     </row>
@@ -5052,9 +5056,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Often article member head prepare.
-Financial agree religious among boy senior.
-Election voice decide.</t>
+          <t>After improve difference.
+Word true true.
+Director situation speak around effect.
+It attack his appear determine.
+Senior action focus outside listen onto draw result.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5064,7 +5070,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-11 06:11:29.545024</t>
+          <t>2024-04-03 22:22:11.086567</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -5087,8 +5093,10 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Network center PM skin win.
-Evening together this news.</t>
+          <t>Win role evening together this news left thing.
+Yet eat interesting.
+Process believe one wish determine.
+Least value opportunity indicate nearly best friend.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5098,7 +5106,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2022-10-22 12:41:22.548338</t>
+          <t>2023-01-07 09:24:53.049860</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -5121,9 +5129,9 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Yet eat interesting.
-Process believe one wish determine.
-Least value opportunity indicate nearly best friend.</t>
+          <t>Behind recognize performance who human without.
+Physical father scientist toward official example media.
+Away read couple husband offer nature.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5133,12 +5141,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2024-05-15 21:58:45.408562</t>
+          <t>2024-02-13 22:28:33.230515</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2024-06-11 21:58:45.408562</t>
+          <t>2024-03-11 22:28:33.230515</t>
         </is>
       </c>
     </row>
@@ -5160,11 +5168,8 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Behind recognize performance who human without.
-Physical father scientist toward official example media.
-Away read couple husband offer nature.
-Stop poor address.
-Red test middle state including.</t>
+          <t>Lawyer red test.
+Various nearly my finally eye of partner.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5174,12 +5179,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2024-02-12 22:53:29.230515</t>
+          <t>2022-09-15 02:22:31.455762</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2024-03-28 22:53:29.230515</t>
+          <t>2022-10-30 02:22:31.455762</t>
         </is>
       </c>
     </row>
@@ -5201,10 +5206,8 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Figure surface science education move.
-Cell over everything safe.
-Use guess who condition case.
-Tax bar method seven you above our factor.</t>
+          <t>Loss cell over everything safe yard use.
+Myself wish generation they personal particularly.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5214,12 +5217,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-26 06:57:37.744652</t>
+          <t>2025-03-02 09:36:14.560968</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-06-21 06:57:37.744652</t>
+          <t>2025-05-28 09:36:14.560968</t>
         </is>
       </c>
     </row>
@@ -5241,8 +5244,8 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Hotel number out.
-Film tend front serve.</t>
+          <t>Above our factor avoid.
+Watch and agreement into six.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5252,7 +5255,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2022-10-28 10:16:28.466324</t>
+          <t>2023-11-09 18:14:21.087088</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -5275,10 +5278,10 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Employee at indeed leave.
-Blood song draw care item training.
-Crime goal decide now book success conference may.
-Soon price present central create.</t>
+          <t>Brother without never chair effect trip.
+Leave purpose her treatment.
+Draw care item training perhaps six listen.
+Now book success conference.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5288,12 +5291,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2023-07-03 03:08:05.824116</t>
+          <t>2023-04-01 14:25:51.924689</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2023-10-21 03:08:05.824116</t>
+          <t>2023-07-20 14:25:51.924689</t>
         </is>
       </c>
     </row>
@@ -5315,8 +5318,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rise heart vote.
-Else fine science offer especially pay material.</t>
+          <t>Price present central create.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5326,7 +5328,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2025-02-25 09:57:25.103862</t>
+          <t>2024-07-13 15:03:25.548378</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -5349,8 +5351,9 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tough hit subject ok.
-Item capital school author us start people wall.</t>
+          <t>Rise heart vote.
+Else fine science offer especially pay material.
+Think this tough hit.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5360,12 +5363,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2025-08-25 15:08:37.160854</t>
+          <t>2025-02-26 09:32:29.103862</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2025-10-13 15:08:37.160854</t>
+          <t>2025-04-16 09:32:29.103862</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5390,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Word food sign perhaps section.</t>
+          <t>Item capital school author us start people wall.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5397,7 +5400,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2023-06-15 19:53:05.403863</t>
+          <t>2025-11-21 20:36:14.407869</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5420,8 +5423,8 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Explain beyond behavior.
-Drive job ahead thing decade.</t>
+          <t>Word food sign perhaps section.
+Any price no determine drive.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5431,12 +5434,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-14 19:01:18.487283</t>
+          <t>2023-06-16 19:28:09.403863</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-05-03 19:01:18.487283</t>
+          <t>2023-09-02 19:28:09.403863</t>
         </is>
       </c>
     </row>
@@ -5458,8 +5461,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Shoulder trade only research data.
-Say force high budget chance author.</t>
+          <t>Decade surface everybody shoulder trade only.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5469,12 +5471,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2025-12-04 23:35:09.705273</t>
+          <t>2024-04-10 00:24:31.966723</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-01-14 23:35:09.705273</t>
+          <t>2024-05-21 00:24:31.966723</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5498,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Week together brother.</t>
+          <t>Indeed oil pay.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5506,7 +5508,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2025-02-07 22:29:52.820455</t>
+          <t>2025-05-20 13:41:03.673214</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -5529,7 +5531,8 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Action be voice participant collection.</t>
+          <t>Pretty everyone reduce agree.
+Together brother huge director action be.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5539,7 +5542,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2024-02-13 13:28:14.384240</t>
+          <t>2023-01-04 14:34:03.119752</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5562,7 +5565,8 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Education produce activity activity born evening.</t>
+          <t>Collection affect tax have foreign seem.
+Culture nice process.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5572,12 +5576,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2022-08-09 03:10:13.665079</t>
+          <t>2026-04-12 17:01:14.170291</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2022-10-01 03:10:13.665079</t>
+          <t>2026-06-04 17:01:14.170291</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5613,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2025-06-03 08:11:56.142330</t>
+          <t>2023-07-20 21:28:47.969587</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -5642,7 +5646,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2023-04-04 11:16:15.191170</t>
+          <t>2023-04-05 10:51:19.191170</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5676,7 +5680,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2025-12-04 20:05:40.231177</t>
+          <t>2025-12-05 19:40:44.231177</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5713,12 +5717,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2023-11-20 23:20:54.623562</t>
+          <t>2023-11-21 22:55:58.623562</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2024-01-06 23:20:54.623562</t>
+          <t>2024-01-07 22:55:58.623562</t>
         </is>
       </c>
     </row>
@@ -5751,12 +5755,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2024-12-28 18:01:46.148246</t>
+          <t>2024-12-29 17:36:50.148246</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2025-02-21 18:01:46.148246</t>
+          <t>2025-02-22 17:36:50.148246</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5793,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2025-07-28 08:59:06.665273</t>
+          <t>2025-07-29 08:34:10.665273</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2025-11-09 08:59:06.665273</t>
+          <t>2025-11-10 08:34:10.665273</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5830,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2023-01-26 11:34:11.246946</t>
+          <t>2023-01-27 11:09:15.246946</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2023-04-24 11:34:11.246946</t>
+          <t>2023-04-25 11:09:15.246946</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5868,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2023-03-10 10:37:40.436031</t>
+          <t>2023-03-11 10:12:44.436031</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2023-03-25 10:37:40.436031</t>
+          <t>2023-03-26 10:12:44.436031</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5905,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2024-05-29 13:13:48.659000</t>
+          <t>2024-05-30 12:48:52.659000</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2024-06-19 13:13:48.659000</t>
+          <t>2024-06-20 12:48:52.659000</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5943,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2023-02-20 14:47:24.017594</t>
+          <t>2023-02-21 14:22:28.017594</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2023-06-03 14:47:24.017594</t>
+          <t>2023-06-04 14:22:28.017594</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5981,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2024-04-13 09:30:46.463435</t>
+          <t>2024-04-14 09:05:50.463435</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -6011,7 +6015,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2024-12-28 22:43:32.733707</t>
+          <t>2024-12-29 22:18:36.733707</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -6045,12 +6049,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2025-10-11 11:34:41.732568</t>
+          <t>2025-10-12 11:09:45.732568</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2025-10-13 11:34:41.732568</t>
+          <t>2025-10-14 11:09:45.732568</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6089,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2025-09-04 23:14:58.472327</t>
+          <t>2025-09-05 22:50:02.472327</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2025-10-23 23:14:58.472327</t>
+          <t>2025-10-24 22:50:02.472327</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6128,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2022-11-16 13:17:11.049045</t>
+          <t>2022-11-17 12:52:15.049045</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -6157,7 +6161,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2023-02-20 15:22:24.325842</t>
+          <t>2023-02-21 14:57:28.325842</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -6170,7 +6174,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6191,12 +6195,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2025-10-07 11:56:01.932849</t>
+          <t>2025-10-08 11:31:05.932849</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-01-27 11:56:01.932849</t>
+          <t>2026-01-28 11:31:05.932849</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6232,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2023-02-03 03:07:07.272830</t>
+          <t>2023-02-04 02:42:11.272830</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2023-02-10 03:07:07.272830</t>
+          <t>2023-02-11 02:42:11.272830</t>
         </is>
       </c>
     </row>
@@ -6267,12 +6271,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2023-10-13 13:22:03.993841</t>
+          <t>2023-10-14 12:57:07.993841</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2024-01-11 13:22:03.993841</t>
+          <t>2024-01-12 12:57:07.993841</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6311,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2025-04-04 04:13:44.341869</t>
+          <t>2025-04-05 03:48:48.341869</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -6340,7 +6344,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-03 22:38:30.368639</t>
+          <t>2026-03-04 22:13:34.368639</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2025-09-28 02:39:44.874257</t>
+          <t>2025-09-29 02:14:48.874257</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -6406,7 +6410,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2024-06-18 23:58:16.091727</t>
+          <t>2024-06-19 23:33:20.091727</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6442,7 +6446,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2025-05-18 21:55:19.560671</t>
+          <t>2025-05-19 21:30:23.560671</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -6478,12 +6482,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2023-07-08 01:06:18.462795</t>
+          <t>2023-07-09 00:41:22.462795</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2023-09-09 01:06:18.462795</t>
+          <t>2023-09-10 00:41:22.462795</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6523,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2023-10-26 10:14:31.115016</t>
+          <t>2023-10-27 09:49:35.115016</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2024-02-18 10:14:31.115016</t>
+          <t>2024-02-19 09:49:35.115016</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6562,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2024-01-04 14:40:46.099306</t>
+          <t>2024-01-05 14:15:50.099306</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2024-02-13 14:40:46.099306</t>
+          <t>2024-02-14 14:15:50.099306</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2025-10-18 11:22:21.108843</t>
+          <t>2025-10-19 10:57:25.108843</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
@@ -6629,7 +6633,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2023-01-30 06:48:56.260088</t>
+          <t>2023-01-31 06:24:00.260088</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -6662,7 +6666,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2022-11-16 06:43:17.800785</t>
+          <t>2022-11-17 06:18:21.800785</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -6696,12 +6700,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2025-12-04 17:59:43.110332</t>
+          <t>2025-12-05 17:34:47.110332</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-01-18 17:59:43.110332</t>
+          <t>2026-01-19 17:34:47.110332</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6737,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2023-06-16 04:18:07.853262</t>
+          <t>2023-06-17 03:53:11.853262</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2023-08-29 04:18:07.853262</t>
+          <t>2023-08-30 03:53:11.853262</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6775,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2024-07-19 13:33:27.130776</t>
+          <t>2024-07-20 13:08:31.130776</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2024-11-02 13:33:27.130776</t>
+          <t>2024-11-03 13:08:31.130776</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6813,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2025-05-12 21:02:43.676232</t>
+          <t>2025-05-13 20:37:47.676232</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2025-06-12 21:02:43.676232</t>
+          <t>2025-06-13 20:37:47.676232</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6851,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2022-08-04 11:55:59.773015</t>
+          <t>2022-08-05 11:31:03.773015</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -6881,12 +6885,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2025-11-29 18:00:10.210433</t>
+          <t>2025-11-30 17:35:14.210433</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-03-21 18:00:10.210433</t>
+          <t>2026-03-22 17:35:14.210433</t>
         </is>
       </c>
     </row>
@@ -6918,12 +6922,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2025-12-15 13:57:52.175167</t>
+          <t>2025-12-16 13:32:56.175167</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-03-24 13:57:52.175167</t>
+          <t>2026-03-25 13:32:56.175167</t>
         </is>
       </c>
     </row>
@@ -6956,12 +6960,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2023-07-03 00:01:17.526634</t>
+          <t>2023-07-03 23:36:21.526634</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2023-06-10 00:01:17.526634</t>
+          <t>2023-06-10 23:36:21.526634</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6999,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2024-01-16 06:56:25.462050</t>
+          <t>2024-01-17 06:31:29.462050</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -7030,12 +7034,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2024-12-26 15:08:19.742724</t>
+          <t>2024-12-27 14:43:23.742724</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2025-03-19 15:08:19.742724</t>
+          <t>2025-03-20 14:43:23.742724</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7071,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2023-12-17 08:05:47.643649</t>
+          <t>2023-12-18 07:40:51.643649</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -7100,12 +7104,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2025-11-11 05:11:50.628488</t>
+          <t>2025-11-12 04:46:54.628488</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2025-12-30 05:11:50.628488</t>
+          <t>2025-12-31 04:46:54.628488</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7144,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2024-11-23 07:33:13.685650</t>
+          <t>2024-11-24 07:08:17.685650</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -7175,12 +7179,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2023-08-07 06:18:08.168122</t>
+          <t>2023-08-08 05:53:12.168122</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2023-08-08 06:18:08.168122</t>
+          <t>2023-08-09 05:53:12.168122</t>
         </is>
       </c>
     </row>
@@ -7213,12 +7217,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2025-09-24 18:30:09.967723</t>
+          <t>2025-09-25 18:05:13.967723</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2025-11-26 18:30:09.967723</t>
+          <t>2025-11-27 18:05:13.967723</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7256,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-05-29 04:27:29.322266</t>
+          <t>2026-05-30 04:02:33.322266</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -7286,12 +7290,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2023-03-15 13:34:04.048318</t>
+          <t>2023-03-16 13:09:08.048318</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2023-02-20 13:34:04.048318</t>
+          <t>2023-02-21 13:09:08.048318</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7328,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2024-04-16 10:33:48.686905</t>
+          <t>2024-04-17 10:08:52.686905</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
@@ -7359,12 +7363,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2024-01-25 00:47:54.927724</t>
+          <t>2024-01-26 00:22:58.927724</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2024-03-24 00:47:54.927724</t>
+          <t>2024-03-25 00:22:58.927724</t>
         </is>
       </c>
     </row>
@@ -7397,12 +7401,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2023-11-17 13:50:26.851708</t>
+          <t>2023-11-18 13:25:30.851708</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2024-01-17 13:50:26.851708</t>
+          <t>2024-01-18 13:25:30.851708</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7442,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2023-06-25 20:01:08.604624</t>
+          <t>2023-06-26 19:36:12.604624</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
@@ -7472,7 +7476,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2023-06-28 07:10:54.996281</t>
+          <t>2023-06-29 06:45:58.996281</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
@@ -7506,7 +7510,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2023-09-21 07:54:40.620314</t>
+          <t>2023-09-22 07:29:44.620314</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
@@ -7542,7 +7546,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2024-03-26 14:57:47.124839</t>
+          <t>2024-03-27 14:32:51.124839</t>
         </is>
       </c>
       <c r="G196" t="inlineStr"/>
@@ -7575,12 +7579,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-06-19 14:13:52.594452</t>
+          <t>2026-06-20 13:48:56.594452</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-09 14:13:52.594452</t>
+          <t>2026-07-10 13:48:56.594452</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7616,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2025-05-11 16:47:23.769248</t>
+          <t>2025-05-12 16:22:27.769248</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2025-07-17 16:47:23.769248</t>
+          <t>2025-07-18 16:22:27.769248</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7654,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2023-06-05 17:55:26.469753</t>
+          <t>2023-06-06 17:30:30.469753</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2023-05-16 17:55:26.469753</t>
+          <t>2023-05-17 17:30:30.469753</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7691,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2024-03-09 02:22:28.828002</t>
+          <t>2024-03-10 01:57:32.828002</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2024-06-21 02:22:28.828002</t>
+          <t>2024-06-22 01:57:32.828002</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7728,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2025-03-13 14:24:13.995406</t>
+          <t>2025-03-14 13:59:17.995406</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2025-04-16 14:24:13.995406</t>
+          <t>2025-04-17 13:59:17.995406</t>
         </is>
       </c>
     </row>
@@ -7761,12 +7765,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2023-10-11 13:00:26.100362</t>
+          <t>2023-10-12 12:35:30.100362</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2023-10-26 13:00:26.100362</t>
+          <t>2023-10-27 12:35:30.100362</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7804,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2023-08-16 06:56:22.991862</t>
+          <t>2023-08-17 06:31:26.991862</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
@@ -7833,12 +7837,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2023-03-09 20:25:53.586504</t>
+          <t>2023-03-10 20:00:57.586504</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2023-05-25 20:25:53.586504</t>
+          <t>2023-05-26 20:00:57.586504</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7874,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2023-07-12 06:46:00.255843</t>
+          <t>2023-07-13 06:21:04.255843</t>
         </is>
       </c>
       <c r="G205" t="inlineStr"/>
@@ -7905,7 +7909,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-05-29 19:16:29.363012</t>
+          <t>2026-05-30 18:51:33.363012</t>
         </is>
       </c>
       <c r="G206" t="inlineStr"/>
@@ -7939,7 +7943,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2023-12-13 09:10:56.757071</t>
+          <t>2023-12-14 08:46:00.757071</t>
         </is>
       </c>
       <c r="G207" t="inlineStr"/>
@@ -7973,12 +7977,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2022-10-25 00:45:32.925921</t>
+          <t>2022-10-26 00:20:36.925921</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2022-11-15 00:45:32.925921</t>
+          <t>2022-11-16 00:20:36.925921</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7994,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8010,12 +8014,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2023-07-08 09:27:00.177448</t>
+          <t>2023-07-09 09:02:04.177448</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2023-07-15 09:27:00.177448</t>
+          <t>2023-07-16 09:02:04.177448</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8052,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-01-16 21:21:01.756950</t>
+          <t>2026-01-17 20:56:05.756950</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
@@ -8081,7 +8085,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2024-11-15 22:14:05.334730</t>
+          <t>2024-11-16 21:49:09.334730</t>
         </is>
       </c>
       <c r="G211" t="inlineStr"/>
@@ -8094,7 +8098,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8114,12 +8118,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2023-05-12 05:39:38.891968</t>
+          <t>2023-05-13 05:14:42.891968</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2023-08-08 05:39:38.891968</t>
+          <t>2023-06-19 05:14:42.891968</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8155,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2024-08-28 09:38:57.643827</t>
+          <t>2024-08-29 09:14:01.643827</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
@@ -8188,7 +8192,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-02-21 04:58:34.489272</t>
+          <t>2026-02-22 04:33:38.489272</t>
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2022-10-26 16:41:58.126834</t>
+          <t>2022-10-27 16:17:02.126834</t>
         </is>
       </c>
       <c r="G215" t="inlineStr"/>
@@ -8255,7 +8259,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2023-11-20 18:55:50.636061</t>
+          <t>2023-11-21 18:30:54.636061</t>
         </is>
       </c>
       <c r="G216" t="inlineStr"/>
@@ -8289,12 +8293,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2023-05-16 03:16:18.577211</t>
+          <t>2023-05-17 02:51:22.577211</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2023-08-14 03:16:18.577211</t>
+          <t>2023-08-15 02:51:22.577211</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8330,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2024-09-27 05:06:09.230773</t>
+          <t>2024-09-28 04:41:13.230773</t>
         </is>
       </c>
       <c r="G218" t="inlineStr"/>
@@ -8359,7 +8363,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2025-09-02 16:18:26.445691</t>
+          <t>2025-09-03 15:53:30.445691</t>
         </is>
       </c>
       <c r="G219" t="inlineStr"/>
@@ -8394,12 +8398,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2025-07-24 17:57:49.006239</t>
+          <t>2025-07-25 17:32:53.006239</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2025-08-25 17:57:49.006239</t>
+          <t>2025-08-26 17:32:53.006239</t>
         </is>
       </c>
     </row>
@@ -8432,12 +8436,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-01-05 08:07:18.779567</t>
+          <t>2026-01-06 07:42:22.779567</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-01-16 08:07:18.779567</t>
+          <t>2026-01-17 07:42:22.779567</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8474,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-02-01 20:32:45.920644</t>
+          <t>2026-02-02 20:07:49.920644</t>
         </is>
       </c>
       <c r="G222" t="inlineStr"/>
@@ -8503,12 +8507,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2023-12-09 18:49:40.423389</t>
+          <t>2023-12-10 18:24:44.423389</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2024-04-02 18:49:40.423389</t>
+          <t>2024-04-03 18:24:44.423389</t>
         </is>
       </c>
     </row>
@@ -8540,12 +8544,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2022-11-02 12:02:28.942646</t>
+          <t>2022-11-03 11:37:32.942646</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2022-12-14 12:02:28.942646</t>
+          <t>2022-12-15 11:37:32.942646</t>
         </is>
       </c>
     </row>
@@ -8578,12 +8582,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2022-10-18 20:47:03.133343</t>
+          <t>2022-10-19 20:22:07.133343</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2023-01-15 20:47:03.133343</t>
+          <t>2023-01-16 20:22:07.133343</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8619,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2025-10-28 02:27:10.223611</t>
+          <t>2025-10-29 02:02:14.223611</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2025-11-04 02:27:10.223611</t>
+          <t>2025-11-05 02:02:14.223611</t>
         </is>
       </c>
     </row>
@@ -8653,12 +8657,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2025-08-30 07:42:07.003957</t>
+          <t>2025-08-31 07:17:11.003957</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2025-11-10 07:42:07.003957</t>
+          <t>2025-11-11 07:17:11.003957</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8696,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2022-12-20 13:32:00.863038</t>
+          <t>2022-12-21 13:07:04.863038</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2023-03-19 13:32:00.863038</t>
+          <t>2023-03-20 13:07:04.863038</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8733,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2023-10-12 20:50:56.985109</t>
+          <t>2023-10-13 20:26:00.985109</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2023-11-19 20:50:56.985109</t>
+          <t>2023-11-20 20:26:00.985109</t>
         </is>
       </c>
     </row>
@@ -8766,12 +8770,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2025-06-15 05:43:34.469346</t>
+          <t>2025-06-16 05:18:38.469346</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2025-08-24 05:43:34.469346</t>
+          <t>2025-08-25 05:18:38.469346</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8808,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2024-05-29 09:05:57.415644</t>
+          <t>2024-05-30 08:41:01.415644</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2024-06-15 09:05:57.415644</t>
+          <t>2024-06-16 08:41:01.415644</t>
         </is>
       </c>
     </row>
@@ -8841,12 +8845,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-03-11 07:29:06.909885</t>
+          <t>2026-03-12 07:04:10.909885</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-06-06 07:29:06.909885</t>
+          <t>2026-06-07 07:04:10.909885</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8883,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2023-02-17 01:42:40.870516</t>
+          <t>2023-02-18 01:17:44.870516</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2023-04-25 01:42:40.870516</t>
+          <t>2023-04-26 01:17:44.870516</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8922,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2024-06-02 18:45:35.593480</t>
+          <t>2024-06-03 18:20:39.593480</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2024-06-11 18:45:35.593480</t>
+          <t>2024-06-12 18:20:39.593480</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8959,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2023-06-22 06:30:36.190890</t>
+          <t>2023-06-23 06:05:40.190890</t>
         </is>
       </c>
       <c r="G235" t="inlineStr"/>
@@ -8989,12 +8993,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2024-08-23 06:04:24.637710</t>
+          <t>2024-08-24 05:39:28.637710</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2024-08-08 06:04:24.637710</t>
+          <t>2024-08-09 05:39:28.637710</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9033,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2024-07-26 22:50:49.460924</t>
+          <t>2024-07-27 22:25:53.460924</t>
         </is>
       </c>
       <c r="G237" t="inlineStr"/>
@@ -9065,12 +9069,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-05-24 04:51:23.834880</t>
+          <t>2026-05-25 04:26:27.834880</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-08-22 04:51:23.834880</t>
+          <t>2026-08-23 04:26:27.834880</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9106,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2022-08-30 09:17:00.730657</t>
+          <t>2022-08-31 08:52:04.730657</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
@@ -9137,12 +9141,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2023-07-29 06:07:23.737522</t>
+          <t>2023-07-30 05:42:27.737522</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2023-07-31 06:07:23.737522</t>
+          <t>2023-08-01 05:42:27.737522</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9182,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2025-05-02 21:35:48.177053</t>
+          <t>2025-05-03 21:10:52.177053</t>
         </is>
       </c>
       <c r="G241" t="inlineStr"/>
@@ -9191,7 +9195,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9202,25 +9206,20 @@
       <c r="D242" t="inlineStr">
         <is>
           <t>Reach can western find with picture water business.
-Exactly station their worker Republican national.
-Even common since sister assume less.</t>
+Exactly station their worker Republican national.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Jordan Byrd</t>
+          <t>Dennis Lee</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2023-05-21 06:04:51.015596</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>2023-07-15 06:04:51.015596</t>
-        </is>
-      </c>
+          <t>2023-05-22 05:39:55.015596</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9240,22 +9239,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Few fill early easy try southern other.</t>
+          <t>Since sister assume less meeting among few fill.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Daniel Farmer MD</t>
+          <t>Jennifer Tanner</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2024-07-23 23:10:04.886580</t>
+          <t>2024-02-20 08:58:06.574928</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2024-09-06 23:10:04.886580</t>
+          <t>2024-05-25 08:58:06.574928</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9266,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9277,20 +9276,24 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Foreign place dinner cultural.</t>
+          <t>Try southern other.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Dennis Lee</t>
+          <t>Melissa Osborne</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2024-02-01 07:37:15.440118</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr"/>
+          <t>2023-07-06 13:55:29.847895</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2023-10-10 13:55:29.847895</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9310,7 +9313,8 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Knowledge education record toward fund.
+          <t>Foreign place dinner cultural.
+Box enter near ever check region.
 Fish drop head field writer.</t>
         </is>
       </c>
@@ -9321,12 +9325,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2024-02-12 11:11:54.445944</t>
+          <t>2024-02-02 07:12:19.440118</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2024-04-18 11:11:54.445944</t>
+          <t>2024-04-08 07:12:19.440118</t>
         </is>
       </c>
     </row>
@@ -9360,12 +9364,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2025-11-15 14:19:50.568467</t>
+          <t>2025-11-16 13:54:54.568467</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2025-11-17 14:19:50.568467</t>
+          <t>2025-11-18 13:54:54.568467</t>
         </is>
       </c>
     </row>
@@ -9400,12 +9404,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2024-09-30 09:38:10.905053</t>
+          <t>2024-10-01 09:13:14.905053</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2024-10-05 09:38:10.905053</t>
+          <t>2024-10-06 09:13:14.905053</t>
         </is>
       </c>
     </row>
@@ -9440,12 +9444,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2023-05-20 05:52:58.110272</t>
+          <t>2023-05-21 05:28:02.110272</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2023-06-03 05:52:58.110272</t>
+          <t>2023-06-04 05:28:02.110272</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9481,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2025-11-09 14:54:55.028275</t>
+          <t>2025-11-10 14:29:59.028275</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
@@ -9511,12 +9515,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2023-07-25 07:08:24.175836</t>
+          <t>2023-07-26 06:43:28.175836</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2023-08-14 07:08:24.175836</t>
+          <t>2023-08-15 06:43:28.175836</t>
         </is>
       </c>
     </row>
@@ -9548,12 +9552,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2025-10-06 13:42:33.460823</t>
+          <t>2025-10-07 13:17:37.460823</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2025-09-16 13:42:33.460823</t>
+          <t>2025-09-17 13:17:37.460823</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9590,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2023-04-02 00:50:52.567489</t>
+          <t>2023-04-03 00:25:56.567489</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -9619,12 +9623,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-02-05 02:19:19.622176</t>
+          <t>2026-02-06 01:54:23.622176</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-06-05 02:19:19.622176</t>
+          <t>2026-06-06 01:54:23.622176</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9640,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9656,12 +9660,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2025-03-02 17:05:15.049732</t>
+          <t>2025-03-03 16:40:19.049732</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2025-05-27 17:05:15.049732</t>
+          <t>2025-05-28 16:40:19.049732</t>
         </is>
       </c>
     </row>
@@ -9695,12 +9699,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2022-09-04 01:35:09.399858</t>
+          <t>2022-09-05 01:10:13.399858</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2022-10-11 01:35:09.399858</t>
+          <t>2022-10-12 01:10:13.399858</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9736,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2023-06-30 11:33:44.956470</t>
+          <t>2023-07-01 11:08:48.956470</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
@@ -9766,7 +9770,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2024-02-11 02:39:59.100576</t>
+          <t>2024-02-12 02:15:03.100576</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
@@ -9799,7 +9803,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2025-08-02 12:44:04.439053</t>
+          <t>2025-08-03 12:19:08.439053</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
@@ -9833,7 +9837,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2024-03-25 18:40:50.088983</t>
+          <t>2024-03-26 18:15:54.088983</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
@@ -9868,7 +9872,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2025-01-17 05:39:27.131477</t>
+          <t>2025-01-18 05:14:31.131477</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
@@ -9901,7 +9905,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2023-07-06 22:51:51.194373</t>
+          <t>2023-07-07 22:26:55.194373</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
@@ -9935,12 +9939,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-02-02 19:52:59.455702</t>
+          <t>2026-02-03 19:28:03.455702</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-02-10 19:52:59.455702</t>
+          <t>2026-02-11 19:28:03.455702</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9956,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9963,24 +9967,22 @@
       <c r="D263" t="inlineStr">
         <is>
           <t>Number weight glass cup mind.
-Born part such decision put report.</t>
+Born part such decision put report.
+Small quickly century next various our.
+Occur call travel like education growth.</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Melissa Osborne</t>
+          <t>Justin Baldwin</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-01-01 03:42:03.710594</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>2026-03-04 03:42:03.710594</t>
-        </is>
-      </c>
+          <t>2026-01-02 03:17:07.710594</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9990,7 +9992,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10000,7 +10002,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Road record heart administration.</t>
+          <t>Miss let central leader technology necessary.</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10010,12 +10012,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2024-03-16 11:00:22.912485</t>
+          <t>2023-04-04 20:05:28.527389</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2024-05-18 11:00:22.912485</t>
+          <t>2023-06-03 20:05:28.527389</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10039,8 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Travel like education growth consider turn.</t>
+          <t>Weight event blood range its race.
+Election science pressure represent fight guy.</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -10047,7 +10050,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2024-10-23 11:29:08.751032</t>
+          <t>2023-10-29 05:37:48.158590</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -10070,11 +10073,9 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Let central leader technology necessary.
-Should occur weight event blood range.
-Do stage kitchen name pass surface.
-Fight guy seem enough.
-Site skill station this wind show.</t>
+          <t>Site skill station this wind show.
+Force tonight themselves treatment few feeling paper.
+Program case about.</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -10084,12 +10085,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2024-07-17 01:23:08.566186</t>
+          <t>2025-07-13 07:38:40.776360</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2024-06-17 01:23:08.566186</t>
+          <t>2025-06-13 07:38:40.776360</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10112,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Few feeling paper account dark they his.</t>
+          <t>Challenge air local purpose clearly performance president.</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -10121,12 +10122,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2024-09-17 21:49:18.447238</t>
+          <t>2023-08-01 12:24:36.143211</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2024-12-10 21:49:18.447238</t>
+          <t>2023-10-24 12:24:36.143211</t>
         </is>
       </c>
     </row>
@@ -10148,8 +10149,8 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Our tree process main.
-Performance president stop stand theory.</t>
+          <t>Lawyer also letter hit share who including.
+Eight civil fall pull environmental without.</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -10159,7 +10160,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-02-13 10:09:55.016447</t>
+          <t>2025-11-05 09:56:29.039964</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
@@ -10182,7 +10183,8 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Understand voice ahead daughter argue eight civil.</t>
+          <t>Myself order color kid however where while.
+Not resource security own operation wish.</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -10192,7 +10194,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2024-05-04 23:12:56.718719</t>
+          <t>2022-08-04 03:51:20.542610</t>
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
@@ -10215,8 +10217,8 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Would all key Republican myself.
-Girl see agree good agency whether not resource.</t>
+          <t>Head apply activity decide wind hear.
+Site computer message talk.</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -10226,7 +10228,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2023-09-12 15:45:55.109202</t>
+          <t>2024-07-05 19:45:26.321099</t>
         </is>
       </c>
       <c r="G270" t="inlineStr"/>
@@ -10239,7 +10241,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10249,11 +10251,9 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Operation wish many behavior.
-Debate wait bring same number particularly.
-Site computer message talk.
-Rest available bar education.
-No voice Democrat building become politics recently.</t>
+          <t>Charge total become understand.
+Hand model good like like indeed this.
+Woman others tax sense happen serve.</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -10263,12 +10263,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2025-07-08 19:25:47.483641</t>
+          <t>2022-11-19 13:22:48.057458</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2025-09-22 19:25:47.483641</t>
+          <t>2023-02-03 13:22:48.057458</t>
         </is>
       </c>
     </row>
@@ -10290,10 +10290,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Others tax sense.
-Try father source entire cover check.
-Local like they model policy.
-Worker skin who answer hard.</t>
+          <t>Present term trade local like.
+Oil purpose worker skin who answer hard.
+Campaign continue out among eye bank year role.
+Trial service religious.
+Beyond central police defense.</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -10303,12 +10304,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2025-05-15 17:38:35.424918</t>
+          <t>2024-08-05 23:28:47.562591</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2025-08-22 17:38:35.424918</t>
+          <t>2024-11-12 23:28:47.562591</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10331,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Out among eye bank year role any.</t>
+          <t>Challenge pick sound usually writer partner.</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -10340,12 +10341,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2024-11-21 07:49:16.159614</t>
+          <t>2023-11-27 19:01:20.991709</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2025-02-05 07:49:16.159614</t>
+          <t>2024-02-11 19:01:20.991709</t>
         </is>
       </c>
     </row>
@@ -10367,8 +10368,8 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Card something middle way inside.
-Ago year challenge pick sound usually.</t>
+          <t>Employee account garden arm.
+Management next serve interest that.</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10378,12 +10379,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2025-04-19 08:58:22.358112</t>
+          <t>2024-01-24 06:11:46.403942</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2025-07-22 08:58:22.358112</t>
+          <t>2024-04-27 06:11:46.403942</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10406,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Himself worker available range exist.</t>
+          <t>Difference property factor dream this admit wait.</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10415,12 +10416,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-06-24 08:29:10.457421</t>
+          <t>2025-01-10 15:19:30.030423</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-09-03 08:29:10.457421</t>
+          <t>2025-03-22 15:19:30.030423</t>
         </is>
       </c>
     </row>
@@ -10442,9 +10443,8 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Management next serve interest that.
-Officer likely area marriage cold bring go will.
-Hot should evidence brother young amount never.</t>
+          <t>Range it mention cold.
+Approach white surface some first.</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-03-11 10:30:30.643566</t>
+          <t>2024-02-05 11:51:54.934473</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
@@ -10477,9 +10477,10 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Carry about same.
-First certain inside second far TV force.
-Fly between meeting white.</t>
+          <t>Second far TV.
+Current fly between meeting white almost.
+Part set fear quality notice west.
+Tend bit role pull opportunity behavior along represent.</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10489,7 +10490,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2023-03-13 21:24:11.597210</t>
+          <t>2023-02-08 14:17:18.403812</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
@@ -10512,7 +10513,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Human difficult whole data late collection participant few.</t>
+          <t>Everyone kind lose exist easy scientist service.</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10522,12 +10523,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2022-08-28 22:23:27.160202</t>
+          <t>2024-12-28 06:07:14.390802</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2022-09-13 22:23:27.160202</t>
+          <t>2025-01-13 06:07:14.390802</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10550,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Opportunity behavior along represent.</t>
+          <t>Share power beautiful cut turn yeah protect.</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10559,12 +10560,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2025-12-22 00:54:59.534559</t>
+          <t>2025-07-24 23:11:59.234267</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-04-01 00:54:59.534559</t>
+          <t>2025-11-01 23:11:59.234267</t>
         </is>
       </c>
     </row>
@@ -10585,46 +10586,46 @@
         </is>
       </c>
       <c r="D280" t="inlineStr">
-        <is>
-          <t>Everyone kind lose exist easy scientist service.
-Put natural according stock energy example color assume.</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Jordan Byrd</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>2024-12-27 06:32:10.390802</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>CO-000279</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
         <is>
           <t>Wrong develop six nice number individual sort.
 Ok road Mrs effect.
 Add since method behind job three.</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Jordan Byrd</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:17:59.506813</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CO-000279</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Modern concern his.
+Firm production garden study officer contain develop.</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>Dennis Lee</t>
@@ -10632,7 +10633,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2024-11-29 04:08:38.822242</t>
+          <t>2023-10-17 08:42:35.781011</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -10645,7 +10646,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10655,8 +10656,9 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Modern concern his.
-Firm production garden study officer contain develop.</t>
+          <t>Decision policy rock participant.
+Year above happy wall hotel.
+Camera face activity card decade.</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10666,12 +10668,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2023-10-16 09:07:31.781011</t>
+          <t>2026-05-29 17:13:26.945824</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2023-10-29 09:07:31.781011</t>
+          <t>2026-07-31 17:13:26.945824</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10695,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Decision policy rock participant.</t>
+          <t>Term body system.</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -10703,12 +10705,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-05-28 17:38:22.945824</t>
+          <t>2024-03-18 05:52:32.948630</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-06-05 17:38:22.945824</t>
+          <t>2024-03-26 05:52:32.948630</t>
         </is>
       </c>
     </row>
@@ -10730,8 +10732,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Parent feeling recognize.
-Dinner Mr cost forward financial child.</t>
+          <t>Student dinner recent about specific season.
+Explain inside animal it both bag evidence.
+Middle team social defense water.
+Rise build situation apply.
+Have available detail single but.</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10741,12 +10746,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2023-05-17 02:51:31.024551</t>
+          <t>2022-11-09 12:02:01.508529</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2023-08-29 02:51:31.024551</t>
+          <t>2023-02-21 12:02:01.508529</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10773,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Term body system.</t>
+          <t>Someone necessary site.</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10778,12 +10783,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2024-02-11 04:42:33.651600</t>
+          <t>2026-06-20 04:32:28.240797</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2024-04-17 04:42:33.651600</t>
+          <t>2026-08-25 04:32:28.240797</t>
         </is>
       </c>
     </row>
@@ -10805,8 +10810,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Student dinner recent about specific season.
-Explain inside animal it both bag evidence.</t>
+          <t>Investment to staff sister any.</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10816,12 +10820,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2022-11-08 12:26:57.508529</t>
+          <t>2026-05-28 22:42:26.346893</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2023-02-11 12:26:57.508529</t>
+          <t>2026-08-31 22:42:26.346893</t>
         </is>
       </c>
     </row>
@@ -10843,8 +10847,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Team social defense water avoid few leader financial.
-Detail range pay however tough hold.</t>
+          <t>Couple with focus get care provide sister.</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10854,12 +10857,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2025-02-12 04:48:51.501073</t>
+          <t>2026-05-24 03:27:48.430540</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2025-02-17 04:48:51.501073</t>
+          <t>2026-05-29 03:27:48.430540</t>
         </is>
       </c>
     </row>
@@ -10881,10 +10884,10 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Someone necessary site.
-Entire cup skill never.
-Yourself these area.
-Friend major table thousand season.</t>
+          <t>Free charge ball usually.
+Industry make why bad participant loss however.
+Seem later parent.
+Become enjoy ten more girl.</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -10894,12 +10897,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2025-09-21 01:37:25.794432</t>
+          <t>2025-12-11 16:03:33.577556</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2025-10-26 01:37:25.794432</t>
+          <t>2026-01-15 16:03:33.577556</t>
         </is>
       </c>
     </row>
@@ -10921,8 +10924,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Spend free charge ball usually then.
-Age pretty involve various about culture.</t>
+          <t>Just bank use program indeed.</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -10932,7 +10934,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-01-07 09:43:22.060297</t>
+          <t>2024-11-25 20:08:57.538732</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
@@ -10955,7 +10957,8 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Later parent protect become enjoy ten more girl.</t>
+          <t>Majority unit every because pattern dream.
+Chance computer finish contain present.</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10965,7 +10968,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2024-06-09 08:21:06.833758</t>
+          <t>2023-09-12 01:07:25.253201</t>
         </is>
       </c>
       <c r="G290" t="inlineStr"/>
@@ -10988,7 +10991,9 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Just bank use program indeed.</t>
+          <t>Wish design fill each minute wide.
+Rock court town product however produce.
+Similar my build per.</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10998,12 +11003,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2024-11-24 20:33:53.538732</t>
+          <t>2024-02-20 19:07:44.572353</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2025-02-19 20:33:53.538732</t>
+          <t>2024-05-17 19:07:44.572353</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11030,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Majority unit every because pattern dream.</t>
+          <t>South decision go to nation sometimes.</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11035,7 +11040,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2023-09-11 01:32:21.253201</t>
+          <t>2024-09-05 08:39:52.823252</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
@@ -11058,9 +11063,10 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Democrat listen dark concern.
-Little into since main wide financial.
-Wide group family upon perform never.</t>
+          <t>Think view feeling give body woman.
+Occur reach happen everyone.
+Contain really soon firm particularly suddenly never million.
+Information color build.</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -11070,7 +11076,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-02-06 10:25:05.789272</t>
+          <t>2024-08-28 03:47:30.000474</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
@@ -11093,10 +11099,9 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Similar my build per.
-Instead from have within child involve director.
-Mouth point food it size sometimes.
-Body woman politics occur reach happen.</t>
+          <t>Test old company too though need.
+Artist good wear air.
+Over performance television south cut kitchen.</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -11106,12 +11111,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2025-02-22 16:32:02.548117</t>
+          <t>2022-08-21 15:56:40.751767</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2025-04-05 16:32:02.548117</t>
+          <t>2022-10-02 15:56:40.751767</t>
         </is>
       </c>
     </row>
@@ -11133,8 +11138,8 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Ground garden group open.
-Never million subject information.</t>
+          <t>From reason ten result.
+Expert source hold expert.</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11144,12 +11149,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2023-08-20 10:37:15.049352</t>
+          <t>2023-10-14 11:36:35.323595</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2023-10-22 10:37:15.049352</t>
+          <t>2023-12-16 11:36:35.323595</t>
         </is>
       </c>
     </row>
@@ -11170,74 +11175,6 @@
         </is>
       </c>
       <c r="D296" t="inlineStr">
-        <is>
-          <t>Agree compare test old company too though.
-Small artist good wear air goal radio.
-South cut kitchen fire husband southern from.</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>Andrew Crawford</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>2023-03-17 19:24:21.005795</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>CO-000295</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>in-review</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>critical</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Expert source hold expert.</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Lynn Gomez</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>2025-04-21 00:07:16.019704</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>CO-000296</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
         <is>
           <t>Three beautiful sound live plan crime around.
 Account attention use wall.
@@ -11245,6 +11182,73 @@
 Paper happen over center compare despite.</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Andrew Crawford</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:44:48.670926</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CO-000295</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>in-review</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Admit artist perform color.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Lynn Gomez</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-03-23 15:15:00.752602</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CO-000296</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Decide score hear time.
+Move away or affect scene international.</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>Wesley Montgomery</t>
@@ -11252,12 +11256,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2025-12-29 23:09:44.670926</t>
+          <t>2022-09-03 11:37:08.018008</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-01-26 23:09:44.670926</t>
+          <t>2022-10-01 11:37:08.018008</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11283,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Admit artist perform color.</t>
+          <t>East middle push kind money little customer.</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -11289,7 +11293,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-03-22 15:39:56.752602</t>
+          <t>2024-12-21 16:49:08.997377</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
@@ -11312,8 +11316,9 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Decide score hear time.
-Move away or affect scene international.</t>
+          <t>Unit situation market shake believe.
+When society cell.
+Newspaper culture they language capital.</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11323,12 +11328,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2022-09-02 12:02:04.018008</t>
+          <t>2023-11-10 03:10:59.716209</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2022-09-10 12:02:04.018008</t>
+          <t>2023-11-18 03:10:59.716209</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11355,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>East middle push kind money little customer.</t>
+          <t>Out answer record series big film brother.</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -11360,7 +11365,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2024-12-20 17:14:04.997377</t>
+          <t>2025-01-06 12:39:59.641794</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
@@ -11373,35 +11378,30 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Unit situation market shake believe.
-When society cell.</t>
+          <t>Find care away reflect several.</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Andrew Crawford</t>
+          <t>Jennifer Johns</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2023-11-09 03:35:55.716209</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>2024-01-25 03:35:55.716209</t>
-        </is>
-      </c>
+          <t>2025-07-04 14:57:39.644533</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
